--- a/Team-Data/2012-13/3-2-2012-13.xlsx
+++ b/Team-Data/2012-13/3-2-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -951,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>21</v>
@@ -996,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,43 +1110,43 @@
         <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.441</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N4" t="n">
         <v>0.358</v>
       </c>
       <c r="O4" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P4" t="n">
         <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S4" t="n">
         <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U4" t="n">
         <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1088,31 +1155,31 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>18.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1121,10 +1188,10 @@
         <v>29</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1148,37 +1215,37 @@
         <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
@@ -1419,73 +1486,73 @@
         <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O6" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V6" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1497,22 +1564,22 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1527,7 +1594,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>25</v>
@@ -1676,10 +1743,10 @@
         <v>14</v>
       </c>
       <c r="AM7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
         <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>19</v>
       </c>
       <c r="AF8" t="n">
         <v>19</v>
@@ -1843,7 +1910,7 @@
         <v>19</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
         <v>7</v>
@@ -1852,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1864,10 +1931,10 @@
         <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2037,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>16</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2277,7 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="n">
         <v>19</v>
@@ -2219,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,16 +2384,16 @@
         <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
         <v>0.394</v>
@@ -2335,7 +2402,7 @@
         <v>17.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0.798</v>
@@ -2344,28 +2411,28 @@
         <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
         <v>22.5</v>
       </c>
       <c r="V11" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
         <v>19.4</v>
@@ -2374,13 +2441,13 @@
         <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2392,28 +2459,28 @@
         <v>16</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2428,10 +2495,10 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2771,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
@@ -2783,7 +2850,7 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2795,7 +2862,7 @@
         <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
@@ -2992,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3123,7 +3190,7 @@
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
@@ -3156,7 +3223,7 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3174,7 +3241,7 @@
         <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3302,10 +3369,10 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -3573,58 +3640,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
         <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.509</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J18" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
         <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.349</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R18" t="n">
         <v>12.9</v>
       </c>
       <c r="S18" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U18" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
@@ -3636,25 +3703,25 @@
         <v>7.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z18" t="n">
         <v>19.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
@@ -3663,22 +3730,22 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="n">
         <v>20</v>
@@ -3687,22 +3754,22 @@
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
@@ -3723,7 +3790,7 @@
         <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.298</v>
+        <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P19" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R19" t="n">
         <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>8.199999999999999</v>
@@ -3824,16 +3891,16 @@
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
         <v>95.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3848,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3872,22 +3939,22 @@
         <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
@@ -3902,13 +3969,13 @@
         <v>5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
         <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4094,7 @@
         <v>24</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>22</v>
@@ -4060,13 +4127,13 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,7 +4142,7 @@
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4218,7 +4285,7 @@
         <v>11</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4239,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4397,7 +4464,7 @@
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4576,7 +4643,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
         <v>9</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
         <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.356</v>
+        <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="W24" t="n">
         <v>7.1</v>
@@ -4737,16 +4804,16 @@
         <v>16.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4755,7 +4822,7 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>16</v>
@@ -4767,13 +4834,13 @@
         <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,28 +4861,28 @@
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB24" t="n">
         <v>30</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>26</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
@@ -4973,10 +5040,10 @@
         <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -5029,31 +5096,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.466</v>
+        <v>0.456</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J26" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
         <v>23.7</v>
@@ -5062,52 +5129,52 @@
         <v>0.339</v>
       </c>
       <c r="O26" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P26" t="n">
         <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.777</v>
+        <v>0.78</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
         <v>15.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AA26" t="n">
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.6</v>
+        <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,22 +5186,22 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>26</v>
@@ -5146,19 +5213,19 @@
         <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
         <v>22</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
@@ -5182,7 +5249,7 @@
         <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>16</v>
@@ -5361,7 +5428,7 @@
         <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -5483,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.383</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>81.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.441</v>
@@ -5602,7 +5669,7 @@
         <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N29" t="n">
         <v>0.349</v>
@@ -5623,13 +5690,13 @@
         <v>29</v>
       </c>
       <c r="T29" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U29" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
@@ -5641,19 +5708,19 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>19.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5665,16 +5732,16 @@
         <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
         <v>13</v>
@@ -5853,7 +5920,7 @@
         <v>14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>13</v>
@@ -5883,7 +5950,7 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6044,10 +6111,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6065,7 +6132,7 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
@@ -6077,7 +6144,7 @@
         <v>18</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>14</v>
@@ -6089,7 +6156,7 @@
         <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-2-2012-13</t>
+          <t>2013-03-02</t>
         </is>
       </c>
     </row>
